--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_48_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_48_R5.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0239</v>
+        <v>4.9414</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7086</v>
+        <v>3.2005</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3153</v>
+        <v>1.7409</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7999</v>
+        <v>5.2967</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.5152</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7241</v>
+        <v>5.8119</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3333</v>
+        <v>5.201</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5495</v>
+        <v>0.9585</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7837</v>
+        <v>4.2425</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5334</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>-1.4738</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9403</v>
+        <v>1.5694</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7834</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6726</v>
+        <v>-0.4454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5351</v>
+        <v>0.1772</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1375</v>
+        <v>-0.6227</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0095</v>
+        <v>4.8633</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6973</v>
+        <v>3.7833</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3122</v>
+        <v>1.0801</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2967</v>
+        <v>3.7999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5152</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8119</v>
+        <v>3.7241</v>
       </c>
       <c r="J3" t="n">
-        <v>5.201</v>
+        <v>4.3333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9585</v>
+        <v>1.5495</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2425</v>
+        <v>2.7837</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.5334</v>
       </c>
       <c r="N3" t="n">
         <v>-1.4738</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5694</v>
+        <v>0.9403</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3774</v>
+        <v>0.512</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.326</v>
+        <v>0.6097</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0514</v>
+        <v>-0.0977</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3113</v>
+        <v>3.0302</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6908</v>
+        <v>2.0379</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8816</v>
+        <v>3.0472</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6206</v>
+        <v>0.0793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.261</v>
+        <v>2.9679</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1752</v>
+        <v>1.1963</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2756</v>
+        <v>0.3767</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1005</v>
+        <v>0.8196</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2936</v>
+        <v>1.8508</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6551</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3615</v>
+        <v>2.1483</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0328</v>
+        <v>-1.1767</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2467</v>
+        <v>-0.3457</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2139</v>
+        <v>-0.8309</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3247</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6468</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1504</v>
+        <v>2.9045</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0789</v>
+        <v>0.1801</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0715</v>
+        <v>2.7244</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0472</v>
+        <v>1.8816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0793</v>
+        <v>1.6206</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9679</v>
+        <v>0.261</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1963</v>
+        <v>2.1752</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3767</v>
+        <v>2.2756</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8196</v>
+        <v>-0.1005</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8508</v>
+        <v>-0.2936</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2974</v>
+        <v>-0.6551</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1483</v>
+        <v>0.3615</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0565</v>
+        <v>0.626</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2592</v>
+        <v>0.8063</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7973</v>
+        <v>-0.1803</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3247</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3134</v>
+        <v>2.3049</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2638</v>
+        <v>0.5933</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5772</v>
+        <v>1.7116</v>
       </c>
       <c r="G6" t="n">
         <v>1.5823</v>
@@ -922,13 +922,13 @@
         <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0939</v>
+        <v>-0.1024</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6247</v>
+        <v>0.2324</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4692</v>
+        <v>-0.3347</v>
       </c>
       <c r="V6" t="n">
         <v>2.6805</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3561</v>
+        <v>0.8348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9792</v>
+        <v>1.2898</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6231</v>
+        <v>-0.4551</v>
       </c>
       <c r="G7" t="n">
         <v>2.6492</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6847</v>
+        <v>-1.2061</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7468</v>
+        <v>-0.4362</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9379</v>
+        <v>-0.7699</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2431</v>
+        <v>-0.7822</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.878</v>
+        <v>-1.3498</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6348</v>
+        <v>0.5676</v>
       </c>
       <c r="G8" t="n">
         <v>2.8407</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1634</v>
+        <v>-0.3756</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7863</v>
+        <v>0.3145</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6229</v>
+        <v>-0.6901</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8262</v>
+        <v>-1.3043</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5227</v>
+        <v>-1.1688</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3035</v>
+        <v>-0.1354</v>
       </c>
       <c r="G9" t="n">
         <v>0.8406</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9889</v>
+        <v>-0.467</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.3727</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1809</v>
+        <v>-3.1315</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1042</v>
+        <v>-4.458</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9233</v>
+        <v>1.3266</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8734</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8549</v>
+        <v>0.9043</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0578</v>
+        <v>0.704</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.203</v>
+        <v>0.2003</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.9144</v>
+        <v>13.6611</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3158</v>
+        <v>3.062799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5985</v>
+        <v>10.5986</v>
       </c>
       <c r="G11" t="n">
         <v>17.0648</v>
@@ -1312,13 +1312,13 @@
         <v>15.077</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4777</v>
+        <v>-1.7309</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2211</v>
+        <v>1.968</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.6989</v>
+        <v>-3.6987</v>
       </c>
       <c r="V11" t="n">
         <v>0.6467999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.8338</v>
+        <v>7.9129</v>
       </c>
       <c r="E12" t="n">
-        <v>8.818</v>
+        <v>6.9308</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0158</v>
+        <v>0.9821</v>
       </c>
       <c r="G12" t="n">
         <v>3.5431</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3628</v>
+        <v>1.442</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1339</v>
+        <v>1.2467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2289</v>
+        <v>0.1953</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1122</v>
+        <v>-0.2435</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0305</v>
+        <v>1.4639</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9183</v>
+        <v>-1.7075</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5528</v>
+        <v>-0.6352</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9376</v>
+        <v>0.4322</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3848</v>
+        <v>-1.0673</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8602</v>
+        <v>0.8266</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8234</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>0.0368</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3074</v>
+        <v>-1.4618</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1141</v>
+        <v>-0.3577</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4216</v>
+        <v>-1.1041</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8685</v>
+        <v>0.3943</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4288</v>
+        <v>0.4955</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4397</v>
+        <v>-0.1013</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1418</v>
+        <v>-0.9304</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2771</v>
+        <v>-0.4771</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4639</v>
+        <v>0.9831</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7411</v>
+        <v>-1.4601</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6352</v>
+        <v>1.2811</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4322</v>
+        <v>1.1405</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0673</v>
+        <v>0.1406</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8266</v>
+        <v>2.5358</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7897999999999999</v>
+        <v>1.3948</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0368</v>
+        <v>1.141</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4618</v>
+        <v>-1.2547</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3577</v>
+        <v>-0.2543</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1041</v>
+        <v>-1.0004</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3607</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4955</v>
+        <v>-0.393</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1349</v>
+        <v>-0.293</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6025</v>
+        <v>-0.5668</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.766</v>
+        <v>-1.3844</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1635</v>
+        <v>0.8175</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9038</v>
+        <v>0.5528</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9966</v>
+        <v>0.9376</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9072</v>
+        <v>-0.3848</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4379</v>
+        <v>0.8602</v>
       </c>
       <c r="K15" t="n">
-        <v>0.098</v>
+        <v>0.8234</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5359</v>
+        <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4659</v>
+        <v>-0.3074</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0945</v>
+        <v>0.1141</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3713</v>
+        <v>-0.4216</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5512</v>
+        <v>0.4138</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7774</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2262</v>
+        <v>0.3389</v>
       </c>
       <c r="V15" t="n">
-        <v>1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1899</v>
+        <v>-1.0865</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6292</v>
+        <v>-2.6989</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8191</v>
+        <v>1.6124</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2811</v>
+        <v>-0.0888</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1405</v>
+        <v>-1.8019</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1406</v>
+        <v>1.7131</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5358</v>
+        <v>-0.757</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3948</v>
+        <v>-1.7373</v>
       </c>
       <c r="L16" t="n">
-        <v>1.141</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2547</v>
+        <v>0.6681</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2543</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0004</v>
+        <v>0.7328</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3987</v>
+        <v>0.3941</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7468</v>
+        <v>0.3776</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6519</v>
+        <v>0.0165</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2904</v>
+        <v>-1.1223</v>
       </c>
       <c r="E17" t="n">
         <v>-0.8328</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4575</v>
+        <v>-0.2895</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2922</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1436</v>
+        <v>0.3117</v>
       </c>
       <c r="T17" t="n">
         <v>0.5113</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3677</v>
+        <v>-0.1997</v>
       </c>
       <c r="V17" t="n">
         <v>0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5119</v>
+        <v>-1.2874</v>
       </c>
       <c r="E18" t="n">
         <v>-2.7581</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2462</v>
+        <v>1.4707</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9485</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1896</v>
+        <v>-0.9651</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6642</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5254</v>
+        <v>-0.3009</v>
       </c>
       <c r="V18" t="n">
         <v>0.3943</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6769</v>
+        <v>-1.3388</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5245</v>
+        <v>-1.8276</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8477</v>
+        <v>0.4888</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0888</v>
+        <v>-2.9038</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8019</v>
+        <v>-0.9966</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7131</v>
+        <v>-1.9072</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.757</v>
+        <v>-1.4379</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7373</v>
+        <v>0.098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9802999999999999</v>
+        <v>-1.5359</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6681</v>
+        <v>-1.4659</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.0945</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7328</v>
+        <v>-0.3713</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1964</v>
+        <v>0.8149</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>0.7158</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2517</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9583</v>
+        <v>-1.5652</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2465</v>
+        <v>-2.0106</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2882</v>
+        <v>0.4455</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5073</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7705</v>
+        <v>-0.3774</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8057</v>
+        <v>-0.5698</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0351</v>
+        <v>0.1924</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8102</v>
+        <v>-3.7709</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.816</v>
+        <v>-1.934</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9942</v>
+        <v>-1.8369</v>
       </c>
       <c r="G21" t="n">
         <v>-0.738</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.232</v>
+        <v>-0.1926</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2047</v>
+        <v>0.0868</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4367</v>
+        <v>-0.2794</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5767</v>
+        <v>-4.2393</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9967</v>
+        <v>-3.5249</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.58</v>
+        <v>-0.7144</v>
       </c>
       <c r="G22" t="n">
         <v>-5.58</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0756</v>
+        <v>0.4129</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3031</v>
+        <v>0.7749</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2275</v>
+        <v>-0.362</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7421</v>
+        <v>-4.3432</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0745</v>
+        <v>-3.5411</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6677</v>
+        <v>-0.8021</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7479</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0975</v>
+        <v>1.3014</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4911</v>
+        <v>1.0422</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3936</v>
+        <v>0.2592</v>
       </c>
       <c r="V23" t="n">
         <v>0.5671</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.9144</v>
+        <v>-12.1281</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.1345</v>
+        <v>-11.1346</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7799</v>
+        <v>-0.9934999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-17.0647</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5727</v>
+        <v>1.572700000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-18.6374</v>
@@ -2302,7 +2302,7 @@
         <v>-3.7132</v>
       </c>
       <c r="K24" t="n">
-        <v>4.384800000000001</v>
+        <v>4.3848</v>
       </c>
       <c r="L24" t="n">
         <v>-8.0984</v>
@@ -2326,13 +2326,13 @@
         <v>17.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4777</v>
+        <v>3.264</v>
       </c>
       <c r="T24" t="n">
-        <v>3.698799999999999</v>
+        <v>3.6987</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2213</v>
+        <v>-0.4349</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6469000000000001</v>
